--- a/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
+++ b/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
@@ -22,14 +22,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'구성요약'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성표기_확인품목'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_IAP3_2+0'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_IAP3_2+0'!$A$1:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_IAP3_4+0'!$A$1:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11GHz_IAP3_2+0'!$A$1:$N$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11GHz_IAP3_4+0'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11GHz_IAP3_2+0'!$A$1:$N$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11GHz_IAP3_4+0'!$A$1:$N$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'WTM_WBX_기본구성'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Diversity_옵션'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'공용자재_제외'!$A$1:$F$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'확인필요'!$A$1:$B$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'확인필요'!$A$1:$B$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'산출근거'!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>핵심 품목군: Fan, IDU/Chassis, Interface Card, License, Modem, ODU/RFU</t>
+          <t>핵심 품목군: Fan, IDU/Chassis, Interface Card, License, Modem, ODU/RFU - 단일 이벤트 EVT-003 1건에서 핵심 품목 10개가 함께 관측됨(해당 시트 참조). 아직 독립 반복 이벤트가 없어 '유력 후보'는 아니지만, 공급사 확인 시 우선순위가 높은 후보.</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>핵심 품목군: Fan, IDU/Chassis, License, Modem, ODU/RFU</t>
+          <t>핵심 품목군: Fan, IDU/Chassis, License, Modem, ODU/RFU - 단일 이벤트 EVT-013 1건에서 핵심 품목 7개가 함께 관측됨(해당 시트 참조). 아직 독립 반복 이벤트가 없어 '유력 후보'는 아니지만, 공급사 확인 시 우선순위가 높은 후보.</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>4</v>
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>핵심 품목군: Fan, IDU/Chassis, License, Modem, ODU/RFU</t>
+          <t>핵심 품목군: Fan, IDU/Chassis, License, Modem, ODU/RFU - 단일 이벤트 EVT-008 1건에서 핵심 품목 7개가 함께 관측됨(해당 시트 참조). 아직 독립 반복 이벤트가 없어 '유력 후보'는 아니지만, 공급사 확인 시 우선순위가 높은 후보.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -850,55 +850,55 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9198330(Remote Mount Bracket Assembly for ODU600v2)</t>
+          <t>8GHz_IAP3_2+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=3.5. 관측: 7/2(=3.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=300.0. 관측: 600/2(=300.00); 600/2(=300.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
+          <t>8GHz_IAP3_2+0 - K9208733(VR4 Node License)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=300.0. 관측: 600/2(=300.00); 600/2(=300.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208733(VR4 Node License)</t>
+          <t>8GHz_IAP3_2+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00); 4/2(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
+          <t>8GHz_IAP3_2+0 - K9208715(8GHz ODU IAP3 HIGH)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00); 4/2(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208715(8GHz ODU IAP3 HIGH)</t>
+          <t>8GHz_IAP3_2+0 - K9208714(8GHz ODU IAP3 LOW)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -910,19 +910,19 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208714(8GHz ODU IAP3 LOW)</t>
+          <t>8GHz_IAP3_2+0 - K9208706(GbE4f-AV)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208706(GbE4f-AV)</t>
+          <t>8GHz_IAP3_2+0 - K9208709(16E1-A)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208709(16E1-A)</t>
+          <t>8GHz_IAP3_2+0 - K9208707(GbE4e-AV)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208707(GbE4e-AV)</t>
+          <t>8GHz_IAP3_2+0 - K9208699(FAN-CV)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208699(FAN-CV)</t>
+          <t>8GHz_IAP3_2+0 - K9208698(VR4 1RU CHASSIS)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -970,91 +970,91 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9208698(VR4 1RU CHASSIS)</t>
+          <t>8GHz_IAP3_2+0 - K9193441(AVIAT_ANT-HP-DP-10FT-8)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9188160(CTR 8312 Node License)</t>
+          <t>8GHz_IAP3_2+0 - K9193437(AVIAT_ANT-HP-DP-6FT-8)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9193441(AVIAT_ANT-HP-DP-10FT-8)</t>
+          <t>8GHz_IAP3_2+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
+          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 16/2(=8.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9193437(AVIAT_ANT-HP-DP-6FT-8)</t>
+          <t>8GHz_IAP3_4+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_2+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
+          <t>8GHz_IAP3_4+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 16/2(=8.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
+          <t>8GHz_IAP3_4+0 - K9208728(7/8GHz IAP3 Mounting Bracket)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
+          <t>8GHz_IAP3_4+0 - K9208726(7/8GHz FLAT HYBRID 7.125, Direct, UMT,3.7dB)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208728(7/8GHz IAP3 Mounting Bracket)</t>
+          <t>8GHz_IAP3_4+0 - K9178534(FLEXIBLE WAVEGUIDE, 7.125 - 8.500 GHZ, 1200MM, PDR84 FLANGES)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1066,139 +1066,139 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208726(7/8GHz FLAT HYBRID 7.125, Direct, UMT,3.7dB)</t>
+          <t>8GHz_IAP3_4+0 - K9208733(VR4 Node License)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9178534(FLEXIBLE WAVEGUIDE, 7.125 - 8.500 GHZ, 1200MM, PDR84 FLANGES)</t>
+          <t>8GHz_IAP3_4+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208733(VR4 Node License)</t>
+          <t>8GHz_IAP3_4+0 - K9208715(8GHz ODU IAP3 HIGH)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
+          <t>8GHz_IAP3_4+0 - K9208714(8GHz ODU IAP3 LOW)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208715(8GHz ODU IAP3 HIGH)</t>
+          <t>8GHz_IAP3_4+0 - K9208699(FAN-CV)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208714(8GHz ODU IAP3 LOW)</t>
+          <t>8GHz_IAP3_4+0 - K9208698(VR4 1RU CHASSIS)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208699(FAN-CV)</t>
+          <t>8GHz_IAP3_4+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=60.0. 관측: 240/4(=60.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9208698(VR4 1RU CHASSIS)</t>
+          <t>8GHz_IAP3_4+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
+          <t>11GHz_IAP3_2+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=60.0. 관측: 240/4(=60.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 36/2(=18.00); 120/2(=60.00); 36/2(=18.00)[다중대역]; 36/2(=18.00)[다중대역]; 120/2(=60.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>8GHz_IAP3_4+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
+          <t>11GHz_IAP3_2+0 - K9210637(HAX_MULTI ETHERNET CABLE 75M)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
+          <t>11GHz_IAP3_2+0 - K9210635(HAX_MULTI FIBER CABLE 75M)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 36/2(=18.00); 120/2(=60.00); 36/2(=18.00)[다중대역]; 36/2(=18.00)[다중대역]; 120/2(=60.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210637(HAX_MULTI ETHERNET CABLE 75M)</t>
+          <t>11GHz_IAP3_2+0 - K9210633(HAX_MULTI POWER CABLE 75M)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1210,91 +1210,91 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210635(HAX_MULTI FIBER CABLE 75M)</t>
+          <t>11GHz_IAP3_2+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210633(HAX_MULTI POWER CABLE 75M)</t>
+          <t>11GHz_IAP3_2+0 - K9208730(E1 Single Cable, 15m, for VR4/VR10)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
+          <t>11GHz_IAP3_2+0 - K9204026(HAX_WEATHERPROOFING KIT)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208730(E1 Single Cable, 15m, for VR4/VR10)</t>
+          <t>11GHz_IAP3_2+0 - K9208723(TERMINAL UNIT)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=12.0. 관측: 24/2(=12.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204026(HAX_WEATHERPROOFING KIT)</t>
+          <t>11GHz_IAP3_2+0 - K9208722(U-LINK)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208723(TERMINAL UNIT)</t>
+          <t>11GHz_IAP3_2+0 - K9204029(HAX_MULTI-ETHERNET CABLE 100M)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=12.0. 관측: 24/2(=12.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208722(U-LINK)</t>
+          <t>11GHz_IAP3_2+0 - K9204028(HAX_MULTI-FIBER CABLE 100M)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204029(HAX_MULTI-ETHERNET CABLE 100M)</t>
+          <t>11GHz_IAP3_2+0 - K9204027(HAX_MULTI POWER CABLE 100M)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1306,199 +1306,199 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204028(HAX_MULTI-FIBER CABLE 100M)</t>
+          <t>11GHz_IAP3_2+0 - K9208727(10/11GHz FLAT HYBRID 10.0, Direct, UMT,3.7dB)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 2/2(=1.00); 6/2(=3.00); 2/2(=1.00)[다중대역]; 6/2(=3.00). 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204027(HAX_MULTI POWER CABLE 100M)</t>
+          <t>11GHz_IAP3_2+0 - K9208704(PS-MV)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=14.0. 관측: 28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208727(10/11GHz FLAT HYBRID 10.0, Direct, UMT,3.7dB)</t>
+          <t>11GHz_IAP3_2+0 - K9188159(FLEXIBLE WAVEGUIDE, 10.7 - 11.7 GHZ, 1200MM, PDR100 FLANGES)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 2/2(=1.00); 6/2(=3.00); 2/2(=1.00)[다중대역]; 6/2(=3.00). 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00)[다중대역]. 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208704(PS-MV)</t>
+          <t>11GHz_IAP3_2+0 - K9208725(OBC2 Mounting Bracket expand to 1RF)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=14.0. 관측: 28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9188159(FLEXIBLE WAVEGUIDE, 10.7 - 11.7 GHZ, 1200MM, PDR100 FLANGES)</t>
+          <t>11GHz_IAP3_2+0 - K9208724(OBC2 Mounting Bracket Up to 4RF)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 2/2(=1.00)[다중대역]. 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=5.0. 관측: 10/2(=5.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204023(HAX_CTR8740 DUAL POWER SUPPLY)</t>
+          <t>11GHz_IAP3_2+0 - K9210278(SFP TSoP STM-1/OC3 over Gig-E Module)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 4/2(=2.00); 2/2(=1.00); 12/2(=6.00)[다중대역]; 4/2(=2.00)[다중대역]; 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208725(OBC2 Mounting Bracket expand to 1RF)</t>
+          <t>11GHz_IAP3_2+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 4/2(=2.00); 60/2(=30.00); 50/2(=25.00)[다중대역]; 4/2(=2.00)[다중대역]; 60/2(=30.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208724(OBC2 Mounting Bracket Up to 4RF)</t>
+          <t>11GHz_IAP3_2+0 - K9208734(VR10 Node License)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=5.0. 관측: 10/2(=5.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210278(SFP TSoP STM-1/OC3 over Gig-E Module)</t>
+          <t>11GHz_IAP3_2+0 - K9208711(MC-MV Redundancy)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 4/2(=2.00); 2/2(=1.00); 12/2(=6.00)[다중대역]; 4/2(=2.00)[다중대역]; 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208731(MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10)</t>
+          <t>11GHz_IAP3_2+0 - K9208710(STM1-A)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=변동, 공급사 확인 필요. 관측: 4/2(=2.00); 60/2(=30.00); 50/2(=25.00)[다중대역]; 4/2(=2.00)[다중대역]; 60/2(=30.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 8/2(=4.00)[다중대역]; 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208734(VR10 Node License)</t>
+          <t>11GHz_IAP3_2+0 - K9208707(GbE4e-AV)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 10/2(=5.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208711(MC-MV Redundancy)</t>
+          <t>11GHz_IAP3_2+0 - K9208706(GbE4f-AV)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=15.0. 관측: 30/2(=15.00); 12/2(=6.00)[다중대역]; 30/2(=15.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208710(STM1-A)</t>
+          <t>11GHz_IAP3_2+0 - K9208705(MODEM-AV)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 2/2(=1.00); 8/2(=4.00)[다중대역]; 2/2(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=30.0. 관측: 60/2(=30.00); 50/2(=25.00)[다중대역]; 60/2(=30.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208707(GbE4e-AV)</t>
+          <t>11GHz_IAP3_2+0 - K9208703(TERM-MV)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 10/2(=5.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208706(GbE4f-AV)</t>
+          <t>11GHz_IAP3_2+0 - K9208702(FAN-MV)</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=15.0. 관측: 30/2(=15.00); 12/2(=6.00)[다중대역]; 30/2(=15.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=14.0. 관측: 28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208705(MODEM-AV)</t>
+          <t>11GHz_IAP3_2+0 - K9208701(VR10 MC-MV)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=30.0. 관측: 60/2(=30.00); 50/2(=25.00)[다중대역]; 60/2(=30.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=6.0. 관측: 12/2(=6.00); 8/2(=4.00)[다중대역]; 12/2(=6.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208703(TERM-MV)</t>
+          <t>11GHz_IAP3_2+0 - K9208700(VR10 3RU CHASSIS)</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1510,175 +1510,175 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208702(FAN-MV)</t>
+          <t>11GHz_IAP3_2+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=14.0. 관측: 28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=150.0. 관측: 300/2(=150.00); 5100/2(=2550.00)[다중대역]; 300/2(=150.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208701(VR10 MC-MV)</t>
+          <t>11GHz_IAP3_2+0 - K9198328(Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형)</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=6.0. 관측: 12/2(=6.00); 8/2(=4.00)[다중대역]; 12/2(=6.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9208700(VR10 3RU CHASSIS)</t>
+          <t>11GHz_IAP3_2+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=7.0. 관측: 14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
+          <t>11GHz_IAP3_2+0 - K9204032(HAX_GROUND CONDUCTOR)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=150.0. 관측: 300/2(=150.00); 5100/2(=2550.00)[다중대역]; 300/2(=150.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204034(HAX_CTR8740 NODE LICENSE)</t>
+          <t>11GHz_IAP3_2+0 - K9204030(HAX_PROTECTOR MODULE)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204033(HAX_WTM4500 NODE LICENSE)</t>
+          <t>11GHz_IAP3_2+0 - K9193436(AVIAT_ANT-HP-DP-4FT-11)</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204022(HAX_CTR8740 1RU CHSSIS)</t>
+          <t>11GHz_IAP3_4+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00); 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9198328(Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형)</t>
+          <t>11GHz_IAP3_4+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=8.0. 관측: 16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00); 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
+          <t>11GHz_IAP3_4+0 - K9188159(FLEXIBLE WAVEGUIDE, 10.7 - 11.7 GHZ, 1200MM, PDR100 FLANGES)</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204032(HAX_GROUND CONDUCTOR)</t>
+          <t>11GHz_IAP3_4+0 - K9208729(10/11GHz IAP3 Mounting Bracket)</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9204030(HAX_PROTECTOR MODULE)</t>
+          <t>11GHz_IAP3_4+0 - K9208727(10/11GHz FLAT HYBRID 10.0, Direct, UMT,3.7dB)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]. 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_2+0 - K9193436(AVIAT_ANT-HP-DP-4FT-11)</t>
+          <t>11GHz_IAP3_4+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=0.5. 관측: 1/2(=0.50); 1/2(=0.50). </t>
+          <t>판정수준=참고 후보, 대표수량=150.0. 관측: 600/4(=150.00); 600/4(=150.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9210279(HAX_Gigabit Ethernet SFP)</t>
+          <t>11GHz_IAP3_4+0 - K9208733(VR4 Node License)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=2.0. 관측: 8/4(=2.00); 8/4(=2.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9210281(HAX_커넥터 KIT_IF 케이블 종단용)</t>
+          <t>11GHz_IAP3_4+0 - K9208717(11GHz ODU IAP3 HIGH)</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00); 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9188159(FLEXIBLE WAVEGUIDE, 10.7 - 11.7 GHZ, 1200MM, PDR100 FLANGES)</t>
+          <t>11GHz_IAP3_4+0 - K9208716(11GHz ODU IAP3 LOW)</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1690,173 +1690,53 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9208729(10/11GHz IAP3 Mounting Bracket)</t>
+          <t>11GHz_IAP3_4+0 - K9208705(MODEM-AV)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9208727(10/11GHz FLAT HYBRID 10.0, Direct, UMT,3.7dB)</t>
+          <t>11GHz_IAP3_4+0 - K9208699(FAN-CV)</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
+          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9188147(CTR 8540 Redundant Power Supply Module)</t>
+          <t>11GHz_IAP3_4+0 - K9208698(VR4 1RU CHASSIS)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=0.75. 관측: 3/4(=0.75). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11GHz_IAP3_4+0 - K9090174(HAX_IDU/ODU간 IF 케이블,1Meter)</t>
+          <t>11GHz_IAP3_4+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>판정수준=참고 후보, 대표수량=150.0. 관측: 600/4(=150.00); 600/4(=150.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208733(VR4 Node License)</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208717(11GHz ODU IAP3 HIGH)</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208716(11GHz ODU IAP3 LOW)</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). </t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208705(MODEM-AV)</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=1.0. 관측: 4/4(=1.00); 4/4(=1.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208699(FAN-CV)</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9208698(VR4 1RU CHASSIS)</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50); 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9188160(CTR 8312 Node License)</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=0.5. 관측: 2/4(=0.50). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9188149(CTR 8540 FAN Module)</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=1.75. 관측: 7/4(=1.75). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9188162(CTR 8540 Node License)</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>판정수준=참고 후보, 대표수량=0.25. 관측: 1/4(=0.25). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>11GHz_IAP3_4+0 - K9210280(HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함))</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
           <t>판정수준=참고 후보, 대표수량=4.0. 관측: 16/4(=4.00); 16/4(=4.00). 품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B94"/>
+  <autoFilter ref="A1:B84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2585,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3039,26 +2919,26 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>K9198330</t>
+          <t>K9090174</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Remote Mount Bracket Assembly for ODU600v2</t>
+          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Mount/Bracket</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>설치 필수품목</t>
+          <t>핵심 필수품목</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.5</v>
+        <v>300</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -3066,31 +2946,31 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7/2(=3.50)</t>
+          <t>600/2(=300.00); 600/2(=300.00)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>EVT-002+EVT-003</t>
+          <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4501990138</t>
+          <t>4501997602</t>
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>250000</v>
+        <v>2120</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>237500</v>
+        <v>2000</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -3101,17 +2981,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>K9090174</t>
+          <t>K9208733</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
+          <t>VR4 Node License</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>License</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3120,7 +3000,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -3135,7 +3015,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>600/2(=300.00); 600/2(=300.00)</t>
+          <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3145,14 +3025,14 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4501997602</t>
+          <t>4501997620</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>2120</v>
+        <v>525000</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>2000</v>
+        <v>514500</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -3163,17 +3043,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>K9208733</t>
+          <t>K9208731</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VR4 Node License</t>
+          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3182,7 +3062,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -3197,7 +3077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2/2(=1.00); 2/2(=1.00)</t>
+          <t>4/2(=2.00); 4/2(=2.00)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3207,14 +3087,14 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4501997620</t>
+          <t>4501997619</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>525000</v>
+        <v>59285</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>514500</v>
+        <v>58099</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -3225,17 +3105,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>K9208731</t>
+          <t>K9208715</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
+          <t>8GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3244,7 +3124,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -3259,7 +3139,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 4/2(=2.00)</t>
+          <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3269,30 +3149,26 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4501997619</t>
+          <t>4501997615</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>59285</v>
+        <v>3051169</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>58099</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
+        <v>2990145</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>K9208715</t>
+          <t>K9208714</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 HIGH</t>
+          <t>8GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3331,7 +3207,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4501997615</t>
+          <t>4501997614</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
@@ -3345,17 +3221,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>K9208714</t>
+          <t>K9208706</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>8GHz ODU IAP3 LOW</t>
+          <t>GbE4f-AV</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Interface Card</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3389,26 +3265,30 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4501997614</t>
+          <t>4501997611</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>3051169</v>
+        <v>927754</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>2990145</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+        <v>909199</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>K9208706</t>
+          <t>K9208709</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GbE4f-AV</t>
+          <t>16E1-A</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3447,14 +3327,14 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4501997611</t>
+          <t>4501997613</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>927754</v>
+        <v>950776</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>909199</v>
+        <v>931761</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -3465,12 +3345,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>K9208709</t>
+          <t>K9208707</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>16E1-A</t>
+          <t>GbE4e-AV</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3509,14 +3389,14 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4501997613</t>
+          <t>4501997612</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>950776</v>
+        <v>974141</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>931761</v>
+        <v>954659</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -3527,17 +3407,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>K9208707</t>
+          <t>K9208699</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GbE4e-AV</t>
+          <t>FAN-CV</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3571,14 +3451,14 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4501997612</t>
+          <t>4501997610</t>
         </is>
       </c>
       <c r="L16" s="6" t="n">
-        <v>974141</v>
+        <v>174636</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>954659</v>
+        <v>171143</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -3589,17 +3469,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>K9208699</t>
+          <t>K9208698</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FAN-CV</t>
+          <t>VR4 1RU CHASSIS</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3633,14 +3513,14 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4501997610</t>
+          <t>4501997609</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>174636</v>
+        <v>2442678</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>171143</v>
+        <v>2393824</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -3651,26 +3531,26 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>K9208698</t>
+          <t>K9193441</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VR4 1RU CHASSIS</t>
+          <t>AVIAT_ANT-HP-DP-10FT-8</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3685,7 +3565,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2/2(=1.00); 2/2(=1.00)</t>
+          <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3695,44 +3575,40 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4501997609</t>
+          <t>4501997608</t>
         </is>
       </c>
       <c r="L18" s="6" t="n">
-        <v>2442678</v>
+        <v>9100000</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>2393824</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
+        <v>8827000</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>K9188160</t>
+          <t>K9193437</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CTR 8312 Node License</t>
+          <t>AVIAT_ANT-HP-DP-6FT-8</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -3740,52 +3616,48 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2/2(=1.00)</t>
+          <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>EVT-002+EVT-003</t>
+          <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4501990136</t>
+          <t>4501997607</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>200000</v>
+        <v>5000000</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>196000</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
+        <v>4850000</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>K9193441</t>
+          <t>K9210280</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AVIAT_ANT-HP-DP-10FT-8</t>
+          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Antenna</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3794,7 +3666,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -3809,7 +3681,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1/2(=0.50); 1/2(=0.50)</t>
+          <t>16/2(=8.00); 16/2(=8.00)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3819,139 +3691,23 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4501997608</t>
+          <t>4501997604</t>
         </is>
       </c>
       <c r="L20" s="6" t="n">
-        <v>9100000</v>
+        <v>126070</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>8827000</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>K9193437</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>AVIAT_ANT-HP-DP-6FT-8</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1/2(=0.50); 1/2(=0.50)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>EVT-002+EVT-003, EVT-003</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>4501997607</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>4850000</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>K9210280</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Surge/Grounding</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16/2(=8.00); 16/2(=8.00)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>EVT-002+EVT-003, EVT-003</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4501997604</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>126070</v>
-      </c>
-      <c r="M22" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N22"/>
+  <autoFilter ref="A1:N20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4851,7 +4607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6251,17 +6007,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>K9204023</t>
+          <t>K9208725</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>HAX_CTR8740 DUAL POWER SUPPLY</t>
+          <t>OBC2 Mounting Bracket expand to 1RF</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PDP/Power</t>
+          <t>Mount/Bracket</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6270,7 +6026,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -6278,31 +6034,31 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]</t>
+          <t>8/2(=4.00)[다중대역]</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>EVT-006+EVT-007, EVT-007</t>
+          <t>EVT-006+EVT-007</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4502018898, 4502019460</t>
+          <t>4502018923</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>500000</v>
+        <v>159784</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>485000</v>
+        <v>156588</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -6313,12 +6069,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>K9208725</t>
+          <t>K9208724</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OBC2 Mounting Bracket expand to 1RF</t>
+          <t>OBC2 Mounting Bracket Up to 4RF</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6332,7 +6088,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -6347,7 +6103,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8/2(=4.00)[다중대역]</t>
+          <t>10/2(=5.00)[다중대역]</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6357,14 +6113,14 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4502018923</t>
+          <t>4502018922</t>
         </is>
       </c>
       <c r="L24" s="6" t="n">
-        <v>159784</v>
+        <v>352958</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>156588</v>
+        <v>345899</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -6375,26 +6131,28 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>K9208724</t>
+          <t>K9210278</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>OBC2 Mounting Bracket Up to 4RF</t>
+          <t>SFP TSoP STM-1/OC3 over Gig-E Module</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Mount/Bracket</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>설치 필수품목</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>5</v>
+          <t>핵심 필수품목</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>변동, 공급사 확인 필요</t>
+        </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -6402,31 +6160,31 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10/2(=5.00)[다중대역]</t>
+          <t>4/2(=2.00); 2/2(=1.00); 12/2(=6.00)[다중대역]; 4/2(=2.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>EVT-006+EVT-007</t>
+          <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4502018922</t>
+          <t>4502018894, 4502019456, 4502046115</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>352958</v>
+        <v>1000000</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>345899</v>
+        <v>980000</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -6437,17 +6195,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>K9210278</t>
+          <t>K9208731</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SFP TSoP STM-1/OC3 over Gig-E Module</t>
+          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6473,7 +6231,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 2/2(=1.00); 12/2(=6.00)[다중대역]; 4/2(=2.00)[다중대역]; 2/2(=1.00)</t>
+          <t>4/2(=2.00); 60/2(=30.00); 50/2(=25.00)[다중대역]; 4/2(=2.00)[다중대역]; 60/2(=30.00)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6483,14 +6241,14 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4502018894, 4502019456, 4502046115</t>
+          <t>4502018926, 4502019475, 4502046157</t>
         </is>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1000000</v>
+        <v>59285</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>980000</v>
+        <v>58099</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -6501,17 +6259,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>K9208731</t>
+          <t>K9208734</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MODEM INDOOR JUMBER CABLE, 3m, FOR VR4/VR10</t>
+          <t>VR10 Node License</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>License</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6519,10 +6277,8 @@
           <t>핵심 필수품목</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>변동, 공급사 확인 필요</t>
-        </is>
+      <c r="E27" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -6530,31 +6286,31 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 60/2(=30.00); 50/2(=25.00)[다중대역]; 4/2(=2.00)[다중대역]; 60/2(=30.00)</t>
+          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
+          <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4502018926, 4502019475, 4502046157</t>
+          <t>4502018927, 4502046161</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>59285</v>
+        <v>1050000</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>58099</v>
+        <v>1029000</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -6565,17 +6321,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>K9208734</t>
+          <t>K9208711</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VR10 Node License</t>
+          <t>MC-MV Redundancy</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6609,14 +6365,14 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4502018927, 4502046161</t>
+          <t>4502018919, 4502046147</t>
         </is>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1050000</v>
+        <v>1487695</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1029000</v>
+        <v>1457941</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -6627,17 +6383,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>K9208711</t>
+          <t>K9208710</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MC-MV Redundancy</t>
+          <t>STM1-A</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>Interface Card</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6646,7 +6402,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -6661,7 +6417,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
+          <t>2/2(=1.00); 8/2(=4.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6671,14 +6427,14 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4502018919, 4502046147</t>
+          <t>4502018918, 4502046144</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1487695</v>
+        <v>1232797</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>1457941</v>
+        <v>1208141</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -6689,12 +6445,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>K9208710</t>
+          <t>K9208707</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>STM1-A</t>
+          <t>GbE4e-AV</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6708,7 +6464,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -6723,7 +6479,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2/2(=1.00); 8/2(=4.00)[다중대역]; 2/2(=1.00)</t>
+          <t>14/2(=7.00); 10/2(=5.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6733,14 +6489,14 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4502018918, 4502046144</t>
+          <t>4502018917, 4502046141</t>
         </is>
       </c>
       <c r="L30" s="6" t="n">
-        <v>1232797</v>
+        <v>974141</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>1208141</v>
+        <v>954659</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -6751,12 +6507,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>K9208707</t>
+          <t>K9208706</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GbE4e-AV</t>
+          <t>GbE4f-AV</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6770,7 +6526,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -6785,7 +6541,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14/2(=7.00); 10/2(=5.00)[다중대역]; 14/2(=7.00)</t>
+          <t>30/2(=15.00); 12/2(=6.00)[다중대역]; 30/2(=15.00)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6795,14 +6551,14 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4502018917, 4502046141</t>
+          <t>4502018916, 4502046138</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>974141</v>
+        <v>927754</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>954659</v>
+        <v>909199</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -6813,17 +6569,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>K9208706</t>
+          <t>K9208705</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GbE4f-AV</t>
+          <t>MODEM-AV</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Interface Card</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6832,7 +6588,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -6847,7 +6603,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30/2(=15.00); 12/2(=6.00)[다중대역]; 30/2(=15.00)</t>
+          <t>60/2(=30.00); 50/2(=25.00)[다중대역]; 60/2(=30.00)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6857,14 +6613,14 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4502018916, 4502046138</t>
+          <t>4502018915, 4502046135</t>
         </is>
       </c>
       <c r="L32" s="6" t="n">
-        <v>927754</v>
+        <v>557078</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>909199</v>
+        <v>545936</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -6875,17 +6631,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>K9208705</t>
+          <t>K9208703</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MODEM-AV</t>
+          <t>TERM-MV</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -6894,7 +6650,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -6909,7 +6665,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60/2(=30.00); 50/2(=25.00)[다중대역]; 60/2(=30.00)</t>
+          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -6919,14 +6675,14 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4502018915, 4502046135</t>
+          <t>4502018913, 4502046129</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>557078</v>
+        <v>582357</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>545936</v>
+        <v>570710</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -6937,17 +6693,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>K9208703</t>
+          <t>K9208702</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TERM-MV</t>
+          <t>FAN-MV</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -6956,7 +6712,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -6971,7 +6727,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
+          <t>28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6981,14 +6737,14 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4502018913, 4502046129</t>
+          <t>4502018912, 4502046126</t>
         </is>
       </c>
       <c r="L34" s="6" t="n">
-        <v>582357</v>
+        <v>776790</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>570710</v>
+        <v>761254</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -6999,17 +6755,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>K9208702</t>
+          <t>K9208701</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FAN-MV</t>
+          <t>VR10 MC-MV</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>CPU/Control</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7018,7 +6774,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -7033,7 +6789,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00)</t>
+          <t>12/2(=6.00); 8/2(=4.00)[다중대역]; 12/2(=6.00)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -7043,14 +6799,14 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4502018912, 4502046126</t>
+          <t>4502018911, 4502046124</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>776790</v>
+        <v>1487695</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>761254</v>
+        <v>1457941</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -7061,17 +6817,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>K9208701</t>
+          <t>K9208700</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VR10 MC-MV</t>
+          <t>VR10 3RU CHASSIS</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CPU/Control</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7080,7 +6836,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -7095,7 +6851,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12/2(=6.00); 8/2(=4.00)[다중대역]; 12/2(=6.00)</t>
+          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -7105,14 +6861,14 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4502018911, 4502046124</t>
+          <t>4502018910, 4502046122</t>
         </is>
       </c>
       <c r="L36" s="6" t="n">
-        <v>1487695</v>
+        <v>5244380</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>1457941</v>
+        <v>5139492</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -7123,17 +6879,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>K9208700</t>
+          <t>K9090174</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VR10 3RU CHASSIS</t>
+          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7142,7 +6898,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -7150,31 +6906,31 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
+          <t>300/2(=150.00); 5100/2(=2550.00)[다중대역]; 300/2(=150.00)[다중대역]</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
+          <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4502018910, 4502046122</t>
+          <t>4502018890, 4502019452</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>5244380</v>
+        <v>2120</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>5139492</v>
+        <v>2000</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -7185,12 +6941,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>K9090174</t>
+          <t>K9198328</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
+          <t>Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7204,7 +6960,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -7219,7 +6975,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>300/2(=150.00); 5100/2(=2550.00)[다중대역]; 300/2(=150.00)[다중대역]</t>
+          <t>16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -7229,14 +6985,14 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4502018890, 4502019452</t>
+          <t>4502018895, 4502019458</t>
         </is>
       </c>
       <c r="L38" s="6" t="n">
-        <v>2120</v>
+        <v>130000</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>2000</v>
+        <v>123500</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -7247,26 +7003,26 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>K9204034</t>
+          <t>K9210280</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>HAX_CTR8740 NODE LICENSE</t>
+          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -7281,7 +7037,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]</t>
+          <t>8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -7291,14 +7047,14 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4502018909, 4502019465</t>
+          <t>4502018892, 4502019454</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>2500000</v>
+        <v>126070</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>2425000</v>
+        <v>120000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -7309,22 +7065,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>K9204033</t>
+          <t>K9204032</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM4500 NODE LICENSE</t>
+          <t>HAX_GROUND CONDUCTOR</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
@@ -7353,14 +7109,14 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4502018906, 4502019464</t>
+          <t>4502018905, 4502019463</t>
         </is>
       </c>
       <c r="L40" s="6" t="n">
-        <v>2500000</v>
+        <v>30000</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>2425000</v>
+        <v>29100</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -7371,26 +7127,26 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>K9204022</t>
+          <t>K9204030</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>HAX_CTR8740 1RU CHSSIS</t>
+          <t>HAX_PROTECTOR MODULE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -7405,7 +7161,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4/2(=2.00); 2/2(=1.00)[다중대역]; 4/2(=2.00)[다중대역]</t>
+          <t>8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7415,14 +7171,14 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4502018896, 4502019459</t>
+          <t>4502018904, 4502019462</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>4000000</v>
+        <v>400000</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>3880000</v>
+        <v>388000</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -7433,26 +7189,26 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>K9198328</t>
+          <t>K9193436</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
+          <t>AVIAT_ANT-HP-DP-4FT-11</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -7467,277 +7223,29 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]</t>
+          <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>EVT-006+EVT-007, EVT-007</t>
+          <t>EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4502018895, 4502019458</t>
+          <t>4502046116</t>
         </is>
       </c>
       <c r="L42" s="6" t="n">
-        <v>130000</v>
+        <v>3500000</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>123500</v>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>K9210280</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Surge/Grounding</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>EVT-006+EVT-007, EVT-007</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>4502018892, 4502019454</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>126070</v>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>K9204032</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>HAX_GROUND CONDUCTOR</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Surge/Grounding</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>EVT-006+EVT-007, EVT-007</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>4502018905, 4502019463</t>
-        </is>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="M44" s="6" t="n">
-        <v>29100</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>K9204030</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>HAX_PROTECTOR MODULE</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Surge/Grounding</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>EVT-006+EVT-007, EVT-007</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>4502018904, 4502019462</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>400000</v>
-      </c>
-      <c r="M45" s="6" t="n">
-        <v>388000</v>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>K9193436</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>AVIAT_ANT-HP-DP-4FT-11</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>1/2(=0.50); 1/2(=0.50)</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>EVT-010, EVT-010+EVT-011</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>4502046116</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="M46" s="6" t="n">
         <v>3395000</v>
       </c>
-      <c r="N46" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N46"/>
+  <autoFilter ref="A1:N42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7748,7 +7256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8140,26 +7648,26 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>K9188147</t>
+          <t>K9090174</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CTR 8540 Redundant Power Supply Module</t>
+          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PDP/Power</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>설치 필수품목</t>
+          <t>핵심 필수품목</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.75</v>
+        <v>150</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -8167,31 +7675,31 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3/4(=0.75)</t>
+          <t>600/4(=150.00); 600/4(=150.00)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>EVT-008+EVT-009</t>
+          <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4502033299</t>
+          <t>4502029114</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>500000</v>
+        <v>2120</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>490000</v>
+        <v>2000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -8202,17 +7710,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>K9090174</t>
+          <t>K9208733</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>HAX_IDU/ODU간 IF 케이블,1Meter</t>
+          <t>VR4 Node License</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>License</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -8221,7 +7729,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>150</v>
+        <v>0.5</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -8236,7 +7744,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>600/4(=150.00); 600/4(=150.00)</t>
+          <t>2/4(=0.50); 2/4(=0.50)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8246,14 +7754,14 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4502029114</t>
+          <t>4502029128</t>
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>2120</v>
+        <v>525000</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>2000</v>
+        <v>514500</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -8264,17 +7772,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>K9208733</t>
+          <t>K9208717</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>VR4 Node License</t>
+          <t>11GHz ODU IAP3 HIGH</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>ODU/RFU</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -8283,7 +7791,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -8298,7 +7806,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2/4(=0.50); 2/4(=0.50)</t>
+          <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8308,30 +7816,26 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4502029128</t>
+          <t>4502029124</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>525000</v>
+        <v>3051169</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>514500</v>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
+        <v>2990145</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>K9208717</t>
+          <t>K9208716</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>11GHz ODU IAP3 HIGH</t>
+          <t>11GHz ODU IAP3 LOW</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -8370,7 +7874,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4502029124</t>
+          <t>4502029123</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
@@ -8384,17 +7888,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>K9208716</t>
+          <t>K9208705</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>11GHz ODU IAP3 LOW</t>
+          <t>MODEM-AV</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ODU/RFU</t>
+          <t>Modem</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8428,31 +7932,35 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4502029123</t>
+          <t>4502029122</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>3051169</v>
+        <v>557078</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>2990145</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+        <v>545936</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>K9208705</t>
+          <t>K9208699</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MODEM-AV</t>
+          <t>FAN-CV</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Modem</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -8461,7 +7969,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -8476,7 +7984,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4/4(=1.00); 4/4(=1.00)</t>
+          <t>2/4(=0.50); 2/4(=0.50)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8486,14 +7994,14 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4502029122</t>
+          <t>4502029121</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>557078</v>
+        <v>174636</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>545936</v>
+        <v>171143</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -8504,17 +8012,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>K9208699</t>
+          <t>K9208698</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FAN-CV</t>
+          <t>VR4 1RU CHASSIS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -8548,14 +8056,14 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4502029121</t>
+          <t>4502029120</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>174636</v>
+        <v>2442678</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>171143</v>
+        <v>2393824</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -8566,26 +8074,26 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>K9208698</t>
+          <t>K9210280</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VR4 1RU CHASSIS</t>
+          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>Surge/Grounding</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>핵심 필수품목</t>
+          <t>현장 선택품목</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -8600,7 +8108,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2/4(=0.50); 2/4(=0.50)</t>
+          <t>16/4(=4.00); 16/4(=4.00)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8610,14 +8118,14 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4502029120</t>
+          <t>4502029117</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>2442678</v>
+        <v>126070</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>2393824</v>
+        <v>120000</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -8625,318 +8133,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>K9188144</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>CTR 8312 1RU Chassis</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>IDU/Chassis</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>핵심 필수품목</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3/4(=0.75)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>EVT-008+EVT-009</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>4502033301</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>1470000</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>K9188160</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CTR 8312 Node License</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>핵심 필수품목</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2/4(=0.50)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>EVT-008+EVT-009</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4502033300</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>196000</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>K9188149</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>CTR 8540 FAN Module</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Fan</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>핵심 필수품목</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7/4(=1.75)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>EVT-008+EVT-009</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4502033298</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>196000</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>K9188162</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CTR 8540 Node License</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>핵심 필수품목</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1/4(=0.25)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>EVT-008+EVT-009</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4502033297</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>1470000</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>K9210280</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>HAX_Arrestor KIT("N"형 M,F콘넥터 각1EA 포함)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Surge/Grounding</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>현장 선택품목</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>참고 후보</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16/4(=4.00); 16/4(=4.00)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>EVT-008, EVT-008+EVT-009</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4502029117</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>126070</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:N14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
+++ b/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
@@ -22,10 +22,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'구성요약'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성표기_확인품목'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_IAP3_2+0'!$A$1:$N$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_IAP3_4+0'!$A$1:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11GHz_IAP3_2+0'!$A$1:$N$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11GHz_IAP3_4+0'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_IAP3_2+0'!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_IAP3_4+0'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11GHz_IAP3_2+0'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11GHz_IAP3_4+0'!$A$1:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'WTM_WBX_기본구성'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Diversity_옵션'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'공용자재_제외'!$A$1:$F$13</definedName>
@@ -2465,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2473,15 +2473,16 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2507,50 +2508,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>대표 수량(1개 링크=N ODU쌍 기준)</t>
+          <t>구성비 배수(N당 배수, 절대수량 아님)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>판정수준</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>관측횟수(윈도우, 중복포함)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>독립관측횟수(중복제외, 판정근거)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>관측치 목록(수량/기준)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>근거 이벤트ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>근거 주문번호</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>판매단가</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>매입단가</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2580,39 +2586,42 @@
       <c r="E2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 8/2(=4.00)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4501997605</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>74180</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -2642,39 +2651,42 @@
       <c r="E3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>16/2(=8.00); 16/2(=8.00)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>4501997603</t>
         </is>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -2704,39 +2716,42 @@
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>4501997618</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>199525</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>195535</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -2766,39 +2781,42 @@
       <c r="E5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>6/2(=3.00); 2/2(=1.00); 6/2(=3.00)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>4501990137, 4501997606</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>750000</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>735000</v>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2824,39 +2842,42 @@
       <c r="E6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00); 4/2(=2.00)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4501997617</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>299584</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>293592</v>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2882,39 +2903,42 @@
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>4501997616</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>1160933</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>1137714</v>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2940,39 +2964,42 @@
       <c r="E8" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>600/2(=300.00); 600/2(=300.00)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4501997602</t>
         </is>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>2120</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3002,39 +3029,42 @@
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4501997620</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>525000</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>514500</v>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3064,39 +3094,42 @@
       <c r="E10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00); 4/2(=2.00)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>4501997619</t>
         </is>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>59285</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>58099</v>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3126,39 +3159,42 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4501997615</t>
         </is>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3184,39 +3220,42 @@
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4501997614</t>
         </is>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3242,39 +3281,42 @@
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>4501997611</t>
         </is>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>927754</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>909199</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3304,39 +3346,42 @@
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>4501997613</t>
         </is>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>950776</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>931761</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3366,39 +3411,42 @@
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>4501997612</t>
         </is>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>974141</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>954659</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3428,39 +3476,42 @@
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>4501997610</t>
         </is>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="6" t="n">
         <v>174636</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="N16" s="6" t="n">
         <v>171143</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3490,39 +3541,42 @@
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>4501997609</t>
         </is>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>2442678</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="N17" s="6" t="n">
         <v>2393824</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3552,39 +3606,42 @@
       <c r="E18" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>4501997608</t>
         </is>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="6" t="n">
         <v>9100000</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="N18" s="6" t="n">
         <v>8827000</v>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3610,39 +3667,42 @@
       <c r="E19" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>4501997607</t>
         </is>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>5000000</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>4850000</v>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3668,46 +3728,49 @@
       <c r="E20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>16/2(=8.00); 16/2(=8.00)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>EVT-002+EVT-003, EVT-003</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>4501997604</t>
         </is>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="6" t="n">
         <v>126070</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="N20" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:O20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3718,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3726,15 +3789,16 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3760,50 +3824,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>대표 수량(1개 링크=N ODU쌍 기준)</t>
+          <t>구성비 배수(N당 배수, 절대수량 아님)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>판정수준</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>관측횟수(윈도우, 중복포함)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>독립관측횟수(중복제외, 판정근거)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>관측치 목록(수량/기준)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>근거 이벤트ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>근거 주문번호</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>판매단가</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>매입단가</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3833,39 +3902,42 @@
       <c r="E2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>16/4(=4.00)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4502080972</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>74180</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3895,39 +3967,42 @@
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>8/4(=2.00)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>4502080970</t>
         </is>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -3957,39 +4032,42 @@
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>4502080979</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>299584</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>293592</v>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4015,39 +4093,42 @@
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>4502080978</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>1160933</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>1137714</v>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4073,39 +4154,42 @@
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4502080973</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>750000</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>735000</v>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4131,39 +4215,42 @@
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>4502080981</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>525000</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>514500</v>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -4193,39 +4280,42 @@
       <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>16/4(=4.00)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4502080980</t>
         </is>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>59285</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>58099</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -4255,39 +4345,42 @@
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4502080977</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4313,39 +4406,42 @@
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>4502080976</t>
         </is>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4371,39 +4467,42 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4502080975</t>
         </is>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>174636</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>171143</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -4433,39 +4532,42 @@
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4502080974</t>
         </is>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>2442678</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>2393824</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -4495,39 +4597,42 @@
       <c r="E13" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>240/4(=60.00)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>4502080969</t>
         </is>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>2120</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -4557,46 +4662,49 @@
       <c r="E14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>8/4(=2.00)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EVT-013</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>4502080971</t>
         </is>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>126070</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4607,7 +4715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4615,15 +4723,16 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -4649,50 +4758,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>대표 수량(1개 링크=N ODU쌍 기준)</t>
+          <t>구성비 배수(N당 배수, 절대수량 아님)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>판정수준</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>관측횟수(윈도우, 중복포함)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>독립관측횟수(중복제외, 판정근거)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>관측치 목록(수량/기준)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>근거 이벤트ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>근거 주문번호</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>판매단가</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>매입단가</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -4722,39 +4836,42 @@
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4502018925, 4502019472, 4502046155</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>299584</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>293592</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -4784,39 +4901,42 @@
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>4502019476, 4502046159</t>
         </is>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>525000</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>514500</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -4846,39 +4966,42 @@
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>4502019470, 4502046151</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -4908,39 +5031,42 @@
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>4502019469, 4502046149</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -4970,39 +5096,42 @@
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4502019468, 4502046120</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>174636</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>171143</v>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5032,39 +5161,42 @@
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>유력 후보</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00); 2/2(=1.00)[다중대역]; 2/2(=1.00); 10/2(=5.00)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>4502019466, 4502046118, 4502053151</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>2442678</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>2393824</v>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5096,39 +5228,44 @@
           <t>변동, 공급사 확인 필요</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>변동, 공급사 확인 필요</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>36/2(=18.00); 120/2(=60.00); 36/2(=18.00)[다중대역]; 36/2(=18.00)[다중대역]; 120/2(=60.00)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4502018893, 4502019455, 4502046114</t>
         </is>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>74180</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5158,39 +5295,42 @@
       <c r="E9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4502019487</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>1050000</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>1029000</v>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5220,39 +5360,42 @@
       <c r="E10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>4502019486</t>
         </is>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>565000</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>553700</v>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5282,39 +5425,42 @@
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4502019485</t>
         </is>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>1500000</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>1470000</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5344,39 +5490,42 @@
       <c r="E12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4502018891, 4502019453</t>
         </is>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5406,39 +5555,42 @@
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>4502019474</t>
         </is>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>199525</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>195535</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5468,39 +5620,42 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>4502018899, 4502019461</t>
         </is>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>19400</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5530,39 +5685,42 @@
       <c r="E15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>24/2(=12.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>4502018921</t>
         </is>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>104895</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>102797</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5592,39 +5750,42 @@
       <c r="E16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16/2(=8.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>4502018920</t>
         </is>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="6" t="n">
         <v>109148</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="N16" s="6" t="n">
         <v>106965</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5654,39 +5815,42 @@
       <c r="E17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>4502018903</t>
         </is>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>1400000</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="N17" s="6" t="n">
         <v>1358000</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5716,39 +5880,42 @@
       <c r="E18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>4502018901</t>
         </is>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="6" t="n">
         <v>750000</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="N18" s="6" t="n">
         <v>727500</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5778,39 +5945,42 @@
       <c r="E19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>4502018900</t>
         </is>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>2000000</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>1940000</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5842,39 +6012,44 @@
           <t>변동, 공급사 확인 필요</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>변동, 공급사 확인 필요</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 6/2(=3.00); 2/2(=1.00)[다중대역]; 6/2(=3.00)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>4502019471, 4502046153</t>
         </is>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="6" t="n">
         <v>1160933</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="N20" s="6" t="n">
         <v>1137714</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5904,39 +6079,42 @@
       <c r="E21" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>4502018914, 4502046132</t>
         </is>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="6" t="n">
         <v>638577</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="N21" s="6" t="n">
         <v>625805</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -5966,39 +6144,42 @@
       <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 2/2(=1.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>4502019457</t>
         </is>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="6" t="n">
         <v>750000</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="N22" s="6" t="n">
         <v>735000</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6028,39 +6209,42 @@
       <c r="E23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>4502018923</t>
         </is>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="6" t="n">
         <v>159784</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="N23" s="6" t="n">
         <v>156588</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6090,39 +6274,42 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>10/2(=5.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>4502018922</t>
         </is>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="6" t="n">
         <v>352958</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="N24" s="6" t="n">
         <v>345899</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6154,39 +6341,44 @@
           <t>변동, 공급사 확인 필요</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>변동, 공급사 확인 필요</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00); 2/2(=1.00); 12/2(=6.00)[다중대역]; 4/2(=2.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>4502018894, 4502019456, 4502046115</t>
         </is>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="6" t="n">
         <v>1000000</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="N25" s="6" t="n">
         <v>980000</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6218,39 +6410,44 @@
           <t>변동, 공급사 확인 필요</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>변동, 공급사 확인 필요</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>4/2(=2.00); 60/2(=30.00); 50/2(=25.00)[다중대역]; 4/2(=2.00)[다중대역]; 60/2(=30.00)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>4502018926, 4502019475, 4502046157</t>
         </is>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="6" t="n">
         <v>59285</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="N26" s="6" t="n">
         <v>58099</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6280,39 +6477,42 @@
       <c r="E27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>4502018927, 4502046161</t>
         </is>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="6" t="n">
         <v>1050000</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="N27" s="6" t="n">
         <v>1029000</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6342,39 +6542,42 @@
       <c r="E28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>4502018919, 4502046147</t>
         </is>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="6" t="n">
         <v>1487695</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="N28" s="6" t="n">
         <v>1457941</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6404,39 +6607,42 @@
       <c r="E29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>2/2(=1.00); 8/2(=4.00)[다중대역]; 2/2(=1.00)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>4502018918, 4502046144</t>
         </is>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>1232797</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="N29" s="6" t="n">
         <v>1208141</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6466,39 +6672,42 @@
       <c r="E30" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>14/2(=7.00); 10/2(=5.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>4502018917, 4502046141</t>
         </is>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="6" t="n">
         <v>974141</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="N30" s="6" t="n">
         <v>954659</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6528,39 +6737,42 @@
       <c r="E31" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>30/2(=15.00); 12/2(=6.00)[다중대역]; 30/2(=15.00)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>4502018916, 4502046138</t>
         </is>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="6" t="n">
         <v>927754</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="N31" s="6" t="n">
         <v>909199</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6590,39 +6802,42 @@
       <c r="E32" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>60/2(=30.00); 50/2(=25.00)[다중대역]; 60/2(=30.00)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>4502018915, 4502046135</t>
         </is>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="6" t="n">
         <v>557078</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="N32" s="6" t="n">
         <v>545936</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6652,39 +6867,42 @@
       <c r="E33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>4502018913, 4502046129</t>
         </is>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>582357</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="N33" s="6" t="n">
         <v>570710</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6714,39 +6932,42 @@
       <c r="E34" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>28/2(=14.00); 16/2(=8.00)[다중대역]; 28/2(=14.00)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>4502018912, 4502046126</t>
         </is>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="6" t="n">
         <v>776790</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="N34" s="6" t="n">
         <v>761254</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6776,39 +6997,42 @@
       <c r="E35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>12/2(=6.00); 8/2(=4.00)[다중대역]; 12/2(=6.00)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>4502018911, 4502046124</t>
         </is>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="6" t="n">
         <v>1487695</v>
       </c>
-      <c r="M35" s="6" t="n">
+      <c r="N35" s="6" t="n">
         <v>1457941</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6838,39 +7062,42 @@
       <c r="E36" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>14/2(=7.00); 8/2(=4.00)[다중대역]; 14/2(=7.00)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>4502018910, 4502046122</t>
         </is>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="6" t="n">
         <v>5244380</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="N36" s="6" t="n">
         <v>5139492</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6900,39 +7127,42 @@
       <c r="E37" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>300/2(=150.00); 5100/2(=2550.00)[다중대역]; 300/2(=150.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>4502018890, 4502019452</t>
         </is>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="6" t="n">
         <v>2120</v>
       </c>
-      <c r="M37" s="6" t="n">
+      <c r="N37" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -6962,39 +7192,42 @@
       <c r="E38" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>16/2(=8.00); 4/2(=2.00)[다중대역]; 16/2(=8.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>4502018895, 4502019458</t>
         </is>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="6" t="n">
         <v>130000</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="N38" s="6" t="n">
         <v>123500</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -7024,39 +7257,42 @@
       <c r="E39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 100/2(=50.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>4502018892, 4502019454</t>
         </is>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="6" t="n">
         <v>126070</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="N39" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -7086,39 +7322,42 @@
       <c r="E40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>4502018905, 4502019463</t>
         </is>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="N40" s="6" t="n">
         <v>29100</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -7148,39 +7387,42 @@
       <c r="E41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>8/2(=4.00); 4/2(=2.00)[다중대역]; 8/2(=4.00)[다중대역]</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>EVT-006+EVT-007, EVT-007</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>4502018904, 4502019462</t>
         </is>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="6" t="n">
         <v>400000</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="N41" s="6" t="n">
         <v>388000</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음; 일부 근거 윈도우가 여러 주파수 대역 혼재 - Chassis 귀속 불확실(확인 필요)</t>
         </is>
@@ -7210,42 +7452,45 @@
       <c r="E42" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>1/2(=0.50); 1/2(=0.50)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>EVT-010, EVT-010+EVT-011</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>4502046116</t>
         </is>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="6" t="n">
         <v>3500000</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="N42" s="6" t="n">
         <v>3395000</v>
       </c>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N42"/>
+  <autoFilter ref="A1:O42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7256,7 +7501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7264,15 +7509,16 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7298,50 +7544,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>대표 수량(1개 링크=N ODU쌍 기준)</t>
+          <t>구성비 배수(N당 배수, 절대수량 아님)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>판정수준</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>관측횟수(윈도우, 중복포함)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>독립관측횟수(중복제외, 판정근거)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>관측치 목록(수량/기준)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>근거 이벤트ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>근거 주문번호</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>판매단가</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>매입단가</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -7371,39 +7622,42 @@
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>8/4(=2.00); 8/4(=2.00)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4502029118</t>
         </is>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>74180</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -7433,39 +7687,42 @@
       <c r="E3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>16/4(=4.00); 16/4(=4.00)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>4502029115</t>
         </is>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>17000</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -7495,39 +7752,42 @@
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>4502029119</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>750000</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>735000</v>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7553,39 +7813,42 @@
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>4502029127</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>299584</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>293592</v>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7611,39 +7874,42 @@
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4502029125</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>1160933</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>1137714</v>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -7669,39 +7935,42 @@
       <c r="E7" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>600/4(=150.00); 600/4(=150.00)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>4502029114</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>2120</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -7731,39 +8000,42 @@
       <c r="E8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2/4(=0.50); 2/4(=0.50)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4502029128</t>
         </is>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>525000</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>514500</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -7793,39 +8065,42 @@
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>4502029124</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -7851,39 +8126,42 @@
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>4502029123</t>
         </is>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>3051169</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>2990145</v>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7909,39 +8187,42 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>4/4(=1.00); 4/4(=1.00)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4502029122</t>
         </is>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>557078</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>545936</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -7971,39 +8252,42 @@
       <c r="E12" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2/4(=0.50); 2/4(=0.50)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4502029121</t>
         </is>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="6" t="n">
         <v>174636</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>171143</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -8033,39 +8317,42 @@
       <c r="E13" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2/4(=0.50); 2/4(=0.50)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>4502029120</t>
         </is>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>2442678</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>2393824</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
@@ -8095,46 +8382,49 @@
       <c r="E14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>16/4(=4.00); 16/4(=4.00)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EVT-008, EVT-008+EVT-009</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>4502029117</t>
         </is>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>126070</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>품목 자체에 주파수 표기 없음(Chassis/Modem/License 등 공통성 품목) - 동일 윈도우에 다른 대역이 섞이면 귀속이 불확실할 수 있음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
+++ b/output/04_Aviat_구성방식별_표준BoM_추정_v2.xlsx
@@ -2473,7 +2473,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+          <t>추정 수량(N+0 링크 전체 가정, 양쪽 사이트 합산)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3789,7 +3789,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+          <t>추정 수량(N+0 링크 전체 가정, 양쪽 사이트 합산)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -4723,7 +4723,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+          <t>추정 수량(N+0 링크 전체 가정, 양쪽 사이트 합산)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -7509,7 +7509,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>실제 수량(N+0 링크 전체, 양쪽 사이트 합산)</t>
+          <t>추정 수량(N+0 링크 전체 가정, 양쪽 사이트 합산)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
